--- a/config/generated/templates/HitPlanHit.xlsx
+++ b/config/generated/templates/HitPlanHit.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
   <si>
     <t>@table</t>
   </si>
@@ -40,7 +40,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>df0d9f01c3e44551</t>
+    <t>ba104ad9faac7ac3</t>
   </si>
   <si>
     <t>#name</t>
@@ -64,6 +64,15 @@
     <t>crit_policy</t>
   </si>
   <si>
+    <t>damage_parameter_key_override</t>
+  </si>
+  <si>
+    <t>damage_operation_ratio_decimal</t>
+  </si>
+  <si>
+    <t>toughness_amount_decimal</t>
+  </si>
+  <si>
     <t>#field</t>
   </si>
   <si>
@@ -85,6 +94,9 @@
     <t>enum&lt;CritPolicy&gt;</t>
   </si>
   <si>
+    <t>optional&lt;string&gt;</t>
+  </si>
+  <si>
     <t>#scope</t>
   </si>
   <si>
@@ -95,6 +107,9 @@
   </si>
   <si>
     <t>length=1..32</t>
+  </si>
+  <si>
+    <t>length=1..120</t>
   </si>
   <si>
     <t>#desc</t>
@@ -523,6 +538,9 @@
     <col min="4" max="5" width="20.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="23.7109375" style="5" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="29.7109375" style="5" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="24.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -577,10 +595,19 @@
       <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -599,34 +626,52 @@
       </c>
       <c r="G3" s="5" t="s">
         <v>15</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -644,29 +689,47 @@
         <v>6</v>
       </c>
       <c r="G5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -674,6 +737,9 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/config/generated/templates/HitPlanHit.xlsx
+++ b/config/generated/templates/HitPlanHit.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>@table</t>
   </si>
@@ -40,7 +40,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>ba104ad9faac7ac3</t>
+    <t>5fcb7ca3a0a45c23</t>
   </si>
   <si>
     <t>#name</t>
@@ -73,6 +73,9 @@
     <t>toughness_amount_decimal</t>
   </si>
   <si>
+    <t>ignores_weakness</t>
+  </si>
+  <si>
     <t>#field</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
   </si>
   <si>
     <t>optional&lt;string&gt;</t>
+  </si>
+  <si>
+    <t>optional&lt;bool&gt;</t>
   </si>
   <si>
     <t>#scope</t>
@@ -529,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -541,9 +547,10 @@
     <col min="8" max="8" width="29.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="30.7109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="24.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="24" customHeight="1">
+    <row r="2" spans="1:11" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -604,10 +611,13 @@
       <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>10</v>
@@ -636,42 +646,48 @@
       <c r="J3" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="K3" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -700,36 +716,40 @@
       <c r="J5" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="K5" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>30</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="42" customHeight="1">
+    <row r="7" spans="1:11" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -740,9 +760,10 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." sqref="C8:C1007">
       <formula1>1</formula1>
       <formula2>100</formula2>
@@ -753,6 +774,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: PerTarget, Shared, Never" promptTitle="CritPolicy enum" prompt="Select a value from the dropdown." sqref="G8:G1007">
       <formula1>"PerTarget,Shared,Never"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." sqref="K8:K1007">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/generated/templates/HitPlanHit.xlsx
+++ b/config/generated/templates/HitPlanHit.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>5fcb7ca3a0a45c23</t>
+    <t>df03b94f9ff0afe3</t>
   </si>
   <si>
     <t>#name</t>
@@ -103,7 +103,7 @@
     <t>optional&lt;bool&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
